--- a/artfynd/A 36929-2021 artfynd.xlsx
+++ b/artfynd/A 36929-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 36929-2021 artfynd.xlsx
+++ b/artfynd/A 36929-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1141,434 +1141,6 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>112606490</v>
-      </c>
-      <c r="B6" t="n">
-        <v>78919</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Lomsjö, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q6" t="n">
-        <v>589641</v>
-      </c>
-      <c r="R6" t="n">
-        <v>7114047</v>
-      </c>
-      <c r="S6" t="n">
-        <v>10</v>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>Åsele</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>Åsele</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>2022-10-03</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>2022-10-03</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT6" t="inlineStr"/>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>112606489</v>
-      </c>
-      <c r="B7" t="n">
-        <v>78919</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>Lomsjö, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q7" t="n">
-        <v>589665</v>
-      </c>
-      <c r="R7" t="n">
-        <v>7114033</v>
-      </c>
-      <c r="S7" t="n">
-        <v>10</v>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>Åsele</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>Åsele</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>2022-10-03</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>2022-10-03</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT7" t="inlineStr"/>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>112606488</v>
-      </c>
-      <c r="B8" t="n">
-        <v>78919</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Lomsjö, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q8" t="n">
-        <v>589724</v>
-      </c>
-      <c r="R8" t="n">
-        <v>7114033</v>
-      </c>
-      <c r="S8" t="n">
-        <v>10</v>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>Åsele</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>Åsele</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>2022-10-03</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>2022-10-03</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT8" t="inlineStr"/>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>112606491</v>
-      </c>
-      <c r="B9" t="n">
-        <v>78919</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>Lomsjö, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q9" t="n">
-        <v>589691</v>
-      </c>
-      <c r="R9" t="n">
-        <v>7114063</v>
-      </c>
-      <c r="S9" t="n">
-        <v>10</v>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>Åsele</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>Åsele</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>2022-10-03</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>2022-10-03</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT9" t="inlineStr"/>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
